--- a/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,52</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,6</t>
+          <t>0,32; 5,07</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,25</t>
+          <t>0,31; 4,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,53</t>
+          <t>0,18; 2,66</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,27</t>
+          <t>1,89; 8,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,18</t>
+          <t>2,76; 8,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,93</t>
+          <t>2,73; 6,83</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,02</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,48</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,96</t>
+          <t>0,91; 1,98</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4150</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4238</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2391</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3633</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8290</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>446; 7142</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1875</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2532</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>478; 6340</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>485; 7204</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7497</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12924</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2467; 11127</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>4207; 12791</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7728; 19338</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3692; 12913</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7086; 18619</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12766; 27648</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,07</t>
+          <t>0,34; 5,53</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,18</t>
+          <t>0,33; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,66</t>
+          <t>0,18; 2,75</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,51</t>
+          <t>1,84; 8,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,39</t>
+          <t>2,66; 8,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,83</t>
+          <t>2,88; 6,87</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,98</t>
+          <t>0,57; 2,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>0,89; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,98</t>
+          <t>0,95; 2,0</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4150</t>
+          <t>0; 4191</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4238</t>
+          <t>0; 3296</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3283</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8290</t>
+          <t>0; 7623</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>446; 7142</t>
+          <t>475; 7785</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>0; 1992</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2532</t>
+          <t>0; 1955</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>478; 6340</t>
+          <t>498; 6733</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>485; 7204</t>
+          <t>494; 7455</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2467; 11127</t>
+          <t>2407; 10903</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4207; 12791</t>
+          <t>4060; 12914</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7728; 19338</t>
+          <t>8163; 19447</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3692; 12913</t>
+          <t>3708; 13012</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7086; 18619</t>
+          <t>6626; 17854</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12766; 27648</t>
+          <t>13303; 27969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,53</t>
+          <t>0,33; 6,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,32; 4,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,75</t>
+          <t>0,17; 2,7</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,34</t>
+          <t>2,33; 7,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,47</t>
+          <t>1,54; 8,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,87</t>
+          <t>2,65; 6,81</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,0</t>
+          <t>0,88; 2,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,4</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,0</t>
+          <t>0,93; 2,07</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>766</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>766</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4191</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3296</t>
+          <t>0; 4459</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>826</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2315</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 7839</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7623</t>
+          <t>0; 2906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>475; 7785</t>
+          <t>448; 8299</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>270</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1455</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>0; 1135</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2333</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>440; 6466</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>498; 6733</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>494; 7455</t>
+          <t>435; 6907</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>12562</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2407; 10903</t>
+          <t>3625; 11705</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4060; 12914</t>
+          <t>2153; 11644</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8163; 19447</t>
+          <t>7819; 20075</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18245</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3708; 13012</t>
+          <t>6006; 17843</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6626; 17854</t>
+          <t>3722; 13270</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13303; 27969</t>
+          <t>12043; 26960</t>
         </is>
       </c>
     </row>
